--- a/data/trans_dic/IP25A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,14 +519,13 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -535,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -573,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -629,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -646,62 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40,36%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47,13%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -714,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 45,52</t>
+          <t>31,99; 49,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,22; 50,31</t>
+          <t>34,63; 52,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,86; 53,96</t>
+          <t>39,18; 61,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 36,23</t>
+          <t>28,51; 45,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,18; 40,75</t>
+          <t>32,2; 51,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,13; 48,18</t>
+          <t>42,89; 63,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,23; 59,83</t>
+          <t>32,53; 44,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,92; 32,36</t>
+          <t>36,62; 49,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 40,96</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34,65; 46,77</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40,15; 54,41</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,9; 29,29</t>
+          <t>44,77; 60,21</t>
         </is>
       </c>
     </row>
@@ -786,62 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>32,88%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -854,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,06; 40,8</t>
+          <t>36,32; 44,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 35,51</t>
+          <t>32,57; 40,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,88; 47,06</t>
+          <t>44,67; 53,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 16,26</t>
+          <t>36,48; 44,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,16; 39,17</t>
+          <t>33,53; 41,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,33; 37,6</t>
+          <t>43,36; 51,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,84; 47,22</t>
+          <t>37,81; 43,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,97</t>
+          <t>34,08; 39,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,97; 39,15</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>30,38; 35,47</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40,74; 46,15</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,82; 15,02</t>
+          <t>45,15; 50,57</t>
         </is>
       </c>
     </row>
@@ -926,62 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -994,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,82; 25,46</t>
+          <t>18,58; 29,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,4; 31,7</t>
+          <t>23,13; 35,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,77; 32,75</t>
+          <t>25,92; 38,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 18,61</t>
+          <t>26,46; 39,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 33,48</t>
+          <t>25,17; 37,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,26; 33,15</t>
+          <t>31,1; 43,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,82; 37,64</t>
+          <t>23,65; 32,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 18,7</t>
+          <t>25,38; 33,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,14; 27,86</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22,55; 30,49</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>25,71; 33,9</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,98; 16,81</t>
+          <t>30,37; 38,88</t>
         </is>
       </c>
     </row>
@@ -1066,62 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1134,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 35,54</t>
+          <t>33,28; 39,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,65; 34,63</t>
+          <t>32,47; 39,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,76; 42,71</t>
+          <t>41,56; 48,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 16,23</t>
+          <t>35,3; 41,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,66; 36,48</t>
+          <t>33,32; 39,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,19; 35,82</t>
+          <t>42,34; 48,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,47; 44,47</t>
+          <t>35,07; 39,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,14</t>
+          <t>33,65; 38,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,12; 35,14</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30,28; 34,6</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38,1; 42,5</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,97; 15,62</t>
+          <t>42,89; 47,56</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1061,801 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>33732</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37715</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26202</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28324</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34355</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34125</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62056</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>72070</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>60328</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>27011; 41484</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30020; 45353</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20097; 31800</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21896; 35300</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26219; 41698</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>27377; 40694</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>52462; 72424</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>61560; 83121</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>51540; 69315</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>153778</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>143692</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>206042</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>170188</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>167560</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>212150</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>323966</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>311253</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>418192</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>137591; 168678</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>129078; 159654</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188955; 224324</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154434; 187022</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>150917; 185106</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>194795; 229476</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>303304; 346718</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>288464; 332227</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>393813; 441121</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>35555</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46791</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42960</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46314</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60787</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78515</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>89305</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>107578</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>27948; 44920</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34480; 52205</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38362; 57560</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34683; 51194</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>37984; 56832</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>50390; 70326</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>66568; 91647</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>76122; 101446</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>94160; 120559</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>223065</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>224398</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>279034</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>464536</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>472627</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>586097</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>204283; 241902</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205233; 246614</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>258655; 300004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>222809; 259564</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>227357; 267792</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>285822; 328199</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>436658; 490585</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>442283; 500724</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>556494; 617007</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/IP25A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,99; 49,12</t>
+          <t>30,96; 48,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,63; 52,32</t>
+          <t>34,84; 52,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,18; 61,99</t>
+          <t>39,59; 62,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,51; 45,96</t>
+          <t>28,31; 46,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,2; 51,21</t>
+          <t>33,29; 51,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,89; 63,75</t>
+          <t>43,02; 64,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,53; 44,91</t>
+          <t>32,64; 44,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,62; 49,44</t>
+          <t>36,53; 49,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 60,21</t>
+          <t>45,1; 60,5</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,32; 44,52</t>
+          <t>36,35; 45,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,57; 40,29</t>
+          <t>32,27; 40,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,67; 53,03</t>
+          <t>44,81; 52,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,48; 44,18</t>
+          <t>36,6; 43,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,53; 41,13</t>
+          <t>33,57; 41,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,36; 51,08</t>
+          <t>43,07; 50,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,81; 43,22</t>
+          <t>37,69; 42,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,08; 39,26</t>
+          <t>33,81; 39,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,15; 50,57</t>
+          <t>44,92; 50,78</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,58; 29,86</t>
+          <t>18,44; 29,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 35,02</t>
+          <t>23,05; 36,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,92; 38,88</t>
+          <t>25,81; 38,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,46; 39,06</t>
+          <t>26,02; 39,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,17; 37,66</t>
+          <t>24,76; 37,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,1; 43,41</t>
+          <t>31,35; 44,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,65; 32,56</t>
+          <t>23,63; 31,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 33,82</t>
+          <t>25,37; 34,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,37; 38,88</t>
+          <t>30,02; 39,51</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 39,41</t>
+          <t>33,1; 39,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,47; 39,02</t>
+          <t>32,37; 38,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,56; 48,2</t>
+          <t>41,77; 48,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 41,12</t>
+          <t>35,15; 41,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,32; 39,24</t>
+          <t>33,39; 39,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,34; 48,62</t>
+          <t>42,2; 48,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,07; 39,41</t>
+          <t>34,87; 39,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,65; 38,1</t>
+          <t>33,86; 38,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,89; 47,56</t>
+          <t>43,1; 47,51</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27011; 41484</t>
+          <t>26143; 40931</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30020; 45353</t>
+          <t>30200; 45344</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20097; 31800</t>
+          <t>20310; 31887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21896; 35300</t>
+          <t>21743; 35433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26219; 41698</t>
+          <t>27105; 42252</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27377; 40694</t>
+          <t>27464; 41028</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52462; 72424</t>
+          <t>52637; 71931</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61560; 83121</t>
+          <t>61417; 82713</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51540; 69315</t>
+          <t>51921; 69656</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>137591; 168678</t>
+          <t>137701; 170856</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>129078; 159654</t>
+          <t>127887; 160704</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188955; 224324</t>
+          <t>189556; 222812</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154434; 187022</t>
+          <t>154945; 186015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>150917; 185106</t>
+          <t>151071; 184624</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194795; 229476</t>
+          <t>193479; 228391</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>303304; 346718</t>
+          <t>302388; 344483</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>288464; 332227</t>
+          <t>286177; 334780</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>393813; 441121</t>
+          <t>391850; 442924</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27948; 44920</t>
+          <t>27745; 44494</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34480; 52205</t>
+          <t>34360; 53836</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38362; 57560</t>
+          <t>38202; 56950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34683; 51194</t>
+          <t>34097; 51260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37984; 56832</t>
+          <t>37367; 56047</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50390; 70326</t>
+          <t>50797; 71689</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66568; 91647</t>
+          <t>66524; 89509</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76122; 101446</t>
+          <t>76101; 104182</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94160; 120559</t>
+          <t>93074; 122502</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>204283; 241902</t>
+          <t>203162; 242286</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205233; 246614</t>
+          <t>204560; 244649</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>258655; 300004</t>
+          <t>259939; 298730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222809; 259564</t>
+          <t>221905; 259910</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>227357; 267792</t>
+          <t>227830; 268253</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>285822; 328199</t>
+          <t>284906; 329572</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>436658; 490585</t>
+          <t>434098; 492827</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>442283; 500724</t>
+          <t>445048; 502955</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>556494; 617007</t>
+          <t>559183; 616350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36,88%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42,19%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53,46%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>39,94%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>43,51%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>51,08%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,96; 48,47</t>
+          <t>28,27; 46,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,84; 52,31</t>
+          <t>33,04; 51,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,59; 62,16</t>
+          <t>42,54; 63,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,31; 46,14</t>
+          <t>31,17; 48,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,29; 51,89</t>
+          <t>35,89; 52,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,02; 64,27</t>
+          <t>39,57; 62,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,64; 44,61</t>
+          <t>32,32; 45,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 49,2</t>
+          <t>36,76; 49,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,1; 60,5</t>
+          <t>45,07; 60,44</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>40,59%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>36,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>48,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>40,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,35; 45,1</t>
+          <t>36,64; 44,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,27; 40,55</t>
+          <t>33,15; 40,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,81; 52,67</t>
+          <t>43,29; 51,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 43,94</t>
+          <t>36,67; 45,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 41,02</t>
+          <t>32,38; 40,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,07; 50,84</t>
+          <t>44,6; 52,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,69; 42,94</t>
+          <t>37,51; 43,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,81; 39,56</t>
+          <t>34,14; 39,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,92; 50,78</t>
+          <t>45,16; 50,71</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,52%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>23,63%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>28,84%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>31,61%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,44; 29,57</t>
+          <t>26,64; 38,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 36,12</t>
+          <t>24,61; 36,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,47</t>
+          <t>31,69; 44,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,02; 39,11</t>
+          <t>18,2; 29,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,76; 37,14</t>
+          <t>22,87; 35,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,35; 44,25</t>
+          <t>25,14; 37,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,63; 31,8</t>
+          <t>23,17; 32,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,37; 34,73</t>
+          <t>25,69; 34,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,02; 39,51</t>
+          <t>30,18; 39,14</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,48</t>
+          <t>35,17; 41,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,37; 38,71</t>
+          <t>33,33; 39,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,77; 48,0</t>
+          <t>42,36; 48,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,15; 41,18</t>
+          <t>33,18; 39,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,39; 39,31</t>
+          <t>32,33; 39,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,2; 48,82</t>
+          <t>41,9; 48,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,87; 39,59</t>
+          <t>35,0; 39,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,86; 38,26</t>
+          <t>33,73; 38,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,1; 47,51</t>
+          <t>43,07; 47,32</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28324</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34355</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34125</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>33732</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>37715</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>26202</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28324</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34355</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34125</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26143; 40931</t>
+          <t>21714; 35603</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30200; 45344</t>
+          <t>26904; 42009</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20310; 31887</t>
+          <t>27156; 40722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21743; 35433</t>
+          <t>26319; 40792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27105; 42252</t>
+          <t>31115; 45746</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27464; 41028</t>
+          <t>20299; 32014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52637; 71931</t>
+          <t>52124; 73196</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61417; 82713</t>
+          <t>61796; 83340</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51921; 69656</t>
+          <t>51885; 69589</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>306</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170188</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>167560</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212150</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>153778</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>143692</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>206042</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>170188</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>167560</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>212150</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>137701; 170856</t>
+          <t>155109; 186627</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127887; 160704</t>
+          <t>149194; 184117</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>189556; 222812</t>
+          <t>194447; 230940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154945; 186015</t>
+          <t>138924; 170616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>151071; 184624</t>
+          <t>128327; 160217</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193479; 228391</t>
+          <t>188681; 221208</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>302388; 344483</t>
+          <t>300894; 345666</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>286177; 334780</t>
+          <t>288914; 335310</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>391850; 442924</t>
+          <t>393951; 442353</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42960</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46314</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60787</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>35555</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>42991</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>46791</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42960</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>46314</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60787</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27745; 44494</t>
+          <t>34919; 50917</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34360; 53836</t>
+          <t>37143; 55689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38202; 56950</t>
+          <t>51349; 72506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34097; 51260</t>
+          <t>27383; 44606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37367; 56047</t>
+          <t>34085; 52381</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50797; 71689</t>
+          <t>37208; 55598</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66524; 89509</t>
+          <t>65230; 90675</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76101; 104182</t>
+          <t>77054; 103886</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93074; 122502</t>
+          <t>93577; 121361</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>412</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>279034</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>203162; 242286</t>
+          <t>222024; 260918</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204560; 244649</t>
+          <t>227427; 269734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>259939; 298730</t>
+          <t>285940; 329699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221905; 259910</t>
+          <t>203647; 241490</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>227830; 268253</t>
+          <t>204349; 246544</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>284906; 329572</t>
+          <t>260763; 300181</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>434098; 492827</t>
+          <t>435683; 492189</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>445048; 502955</t>
+          <t>443396; 501711</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>559183; 616350</t>
+          <t>558745; 613965</t>
         </is>
       </c>
     </row>
